--- a/DateBase/orders/Nha Thu_2026-6-24.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-24.xlsx
@@ -521,7 +521,7 @@
         <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
       <c r="F11" t="str">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -581,7 +581,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0187655155351</v>
+        <v>01876551553510</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-24.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -524,9 +524,89 @@
         <v>10</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>403_大飞燕浅蓝色_delphinium light blue_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>506_紫罗兰香槟色_violet champagne_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>899_紫罗兰浅黄_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>505_紫罗兰紫_violet purple_undefined_1bunch</v>
+      </c>
+      <c r="F17" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="C18" t="str" xml:space="preserve">
+        <v xml:space="preserve">508_风铃花白色_Canterbury Bells 
+white_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="C19" t="str" xml:space="preserve">
+        <v xml:space="preserve">414_风铃花粉色_Canterbury Bells
+pink_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="C20" t="str" xml:space="preserve">
+        <v xml:space="preserve">413_风铃花淡紫色_Canterbury Bells
+light purple_undefined_1bunch</v>
+      </c>
+      <c r="F20" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>77_珍爱mini_undefined_Gerbera L._20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -581,7 +661,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01876551553510</v>
+        <v>018765515535105305510510550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-24.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-24.xlsx
@@ -603,6 +603,9 @@
       <c r="C21" t="str">
         <v>77_珍爱mini_undefined_Gerbera L._20stems</v>
       </c>
+      <c r="F21" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -661,7 +664,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>018765515535105305510510550</v>
+        <v>0187655155351053055105105510</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-24.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -607,9 +607,44 @@
         <v>10</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>80_冰清玉洁_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>3</v>
+      </c>
+      <c r="C23" t="str">
+        <v>447_黄金球_craspedia_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L25"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -664,7 +699,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0187655155351053055105105510</v>
+        <v>01876551553510530551051055101052520</v>
       </c>
     </row>
   </sheetData>
